--- a/sample_imports/02_BoMon_Mau.xlsx
+++ b/sample_imports/02_BoMon_Mau.xlsx
@@ -7,7 +7,7 @@
     <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="DuLieuMau" sheetId="1" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
-  <si>
-    <t>MẪU DỮ LIỆU BỘ MÔN</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
   <si>
     <t>MaBoMon</t>
   </si>
@@ -32,37 +29,265 @@
     <t>TruongBoMon</t>
   </si>
   <si>
-    <t>MoTa</t>
-  </si>
-  <si>
-    <t>BMANH</t>
-  </si>
-  <si>
-    <t>Bộ Môn Tiếng Anh</t>
+    <t>CNPM</t>
+  </si>
+  <si>
+    <t>Bộ môn Công nghệ Phần mềm</t>
+  </si>
+  <si>
+    <t>CNTT</t>
+  </si>
+  <si>
+    <t>TS. Trần Anh Dũng</t>
+  </si>
+  <si>
+    <t>HTTT</t>
+  </si>
+  <si>
+    <t>Bộ môn Hệ thống Thông tin</t>
+  </si>
+  <si>
+    <t>TS. Phạm Minh Tuấn</t>
+  </si>
+  <si>
+    <t>ATTT</t>
+  </si>
+  <si>
+    <t>Bộ môn An toàn Thông tin</t>
+  </si>
+  <si>
+    <t>TS. Trịnh Văn Thành</t>
+  </si>
+  <si>
+    <t>MMT</t>
+  </si>
+  <si>
+    <t>Bộ môn Mạng máy tính &amp; Viễn thông</t>
+  </si>
+  <si>
+    <t>TS. Lê Hải Đăng</t>
+  </si>
+  <si>
+    <t>KHMT</t>
+  </si>
+  <si>
+    <t>Bộ môn Khoa học Máy tính</t>
+  </si>
+  <si>
+    <t>PGS.TS. Võ Quốc Phong</t>
+  </si>
+  <si>
+    <t>KHDL</t>
+  </si>
+  <si>
+    <t>Bộ môn Khoa học Dữ liệu &amp; AI</t>
+  </si>
+  <si>
+    <t>TS. Đỗ Anh Minh</t>
+  </si>
+  <si>
+    <t>QTKD_DN</t>
+  </si>
+  <si>
+    <t>Bộ môn Quản trị Doanh nghiệp</t>
+  </si>
+  <si>
+    <t>QTKD</t>
+  </si>
+  <si>
+    <t>TS. Bùi Thu Hà</t>
+  </si>
+  <si>
+    <t>MKT</t>
+  </si>
+  <si>
+    <t>Bộ môn Marketing &amp; Bán hàng</t>
+  </si>
+  <si>
+    <t>TS. Nguyễn Văn An</t>
+  </si>
+  <si>
+    <t>CBTP</t>
+  </si>
+  <si>
+    <t>Bộ môn Chế biến Thực phẩm</t>
+  </si>
+  <si>
+    <t>TP</t>
+  </si>
+  <si>
+    <t>PGS.TS. Đỗ Hoài Nam</t>
+  </si>
+  <si>
+    <t>DBTP</t>
+  </si>
+  <si>
+    <t>Bộ môn Đảm bảo Chất lượng &amp; ATTP</t>
+  </si>
+  <si>
+    <t>TS. Trương Tuyết Mai</t>
+  </si>
+  <si>
+    <t>KTD</t>
+  </si>
+  <si>
+    <t>Bộ môn Kỹ thuật Điện &amp; Năng lượng</t>
+  </si>
+  <si>
+    <t>DDT</t>
+  </si>
+  <si>
+    <t>TS. Vũ Anh Quân</t>
+  </si>
+  <si>
+    <t>DT</t>
+  </si>
+  <si>
+    <t>Bộ môn Điện tử &amp; Điều khiển Tự động</t>
+  </si>
+  <si>
+    <t>TS. Hồ Vĩnh Thắng</t>
+  </si>
+  <si>
+    <t>CTM</t>
+  </si>
+  <si>
+    <t>Bộ môn Chế tạo máy</t>
+  </si>
+  <si>
+    <t>CK</t>
+  </si>
+  <si>
+    <t>TS. Phan Trọng Nghĩa</t>
+  </si>
+  <si>
+    <t>CDT</t>
+  </si>
+  <si>
+    <t>Bộ môn Cơ điện tử &amp; Robot</t>
+  </si>
+  <si>
+    <t>TS. Chu Văn Quân</t>
+  </si>
+  <si>
+    <t>TA_CN</t>
+  </si>
+  <si>
+    <t>Bộ môn Tiếng Anh Chuyên ngành</t>
   </si>
   <si>
     <t>NN</t>
   </si>
   <si>
-    <t>TS. Vũ Minh</t>
-  </si>
-  <si>
-    <t>Bộ môn tiếng Anh chuyên ngành &amp; cơ bản</t>
-  </si>
-  <si>
-    <t>BMQTKD</t>
-  </si>
-  <si>
-    <t>Bộ Môn Quản Trị Tổng Hợp</t>
-  </si>
-  <si>
-    <t>QTKD</t>
-  </si>
-  <si>
-    <t>ThS. Nguyễn Lan</t>
-  </si>
-  <si>
-    <t>Bộ môn phụ trách các chuyên ngành QTKD</t>
+    <t>ThS. Trần Thị Bích</t>
+  </si>
+  <si>
+    <t>TA_CB</t>
+  </si>
+  <si>
+    <t>Bộ môn Tiếng Anh Cơ bản</t>
+  </si>
+  <si>
+    <t>ThS. Hoàng Thị Em</t>
+  </si>
+  <si>
+    <t>KT</t>
+  </si>
+  <si>
+    <t>Bộ môn Kế toán Doanh nghiệp</t>
+  </si>
+  <si>
+    <t>KTTC</t>
+  </si>
+  <si>
+    <t>TS. Đinh Hoàng Xuân</t>
+  </si>
+  <si>
+    <t>TC</t>
+  </si>
+  <si>
+    <t>Bộ môn Tài chính &amp; Thuế</t>
+  </si>
+  <si>
+    <t>TS. Cao Thái Vinh</t>
+  </si>
+  <si>
+    <t>LKTE</t>
+  </si>
+  <si>
+    <t>Bộ môn Luật Kinh tế</t>
+  </si>
+  <si>
+    <t>LUAT</t>
+  </si>
+  <si>
+    <t>TS. Phan Văn Phúc</t>
+  </si>
+  <si>
+    <t>SHUD</t>
+  </si>
+  <si>
+    <t>Bộ môn Công nghệ Sinh học Ứng dụng</t>
+  </si>
+  <si>
+    <t>SH</t>
+  </si>
+  <si>
+    <t>QTDL</t>
+  </si>
+  <si>
+    <t>Bộ môn Quản trị Du lịch &amp; Lữ hành</t>
+  </si>
+  <si>
+    <t>DL</t>
+  </si>
+  <si>
+    <t>TS. Hoàng Yến Linh</t>
+  </si>
+  <si>
+    <t>QTKS</t>
+  </si>
+  <si>
+    <t>Bộ môn Quản trị Khách sạn &amp; Nhà hàng</t>
+  </si>
+  <si>
+    <t>ThS. Mai Tuyết Nga</t>
+  </si>
+  <si>
+    <t>KHMT_MT</t>
+  </si>
+  <si>
+    <t>Bộ môn Khoa học Môi trường</t>
+  </si>
+  <si>
+    <t>MT</t>
+  </si>
+  <si>
+    <t>TS. Bùi Mai Hoa</t>
+  </si>
+  <si>
+    <t>TMDT_SO</t>
+  </si>
+  <si>
+    <t>Bộ môn Kinh tế số &amp; E-Commerce</t>
+  </si>
+  <si>
+    <t>TMDT</t>
+  </si>
+  <si>
+    <t>TS. Võ Duy Hùng</t>
+  </si>
+  <si>
+    <t>LOG_CCU</t>
+  </si>
+  <si>
+    <t>Bộ môn Quản trị Chuỗi cung ứng</t>
+  </si>
+  <si>
+    <t>LOG</t>
+  </si>
+  <si>
+    <t>PGS.TS. Mai Thế Vinh</t>
   </si>
 </sst>
 </file>
@@ -70,7 +295,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="1">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -80,52 +305,16 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="13"/>
-      <color rgb="FF1E3A8A"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <i val="0"/>
-      <strike val="0"/>
-      <u val="none"/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E40AF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -133,54 +322,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF93C5FD"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF93C5FD"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF93C5FD"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF93C5FD"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFE2E8F0"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFE2E8F0"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFE2E8F0"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFE2E8F0"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="1">
     <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
-    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="3" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
-    <xf xfId="0" fontId="0" numFmtId="0" fillId="4" borderId="2" applyFont="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,76 +627,380 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="11.569" bestFit="true" customWidth="true" style="0"/>
-    <col min="2" max="2" width="29.421" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="10.426" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="18.71" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="45.846" bestFit="true" customWidth="true" style="0"/>
+    <col min="1" max="1" width="9.283" bestFit="true" customWidth="true" style="0"/>
+    <col min="2" max="2" width="43.561" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="25.851" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" customHeight="1" ht="28">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" customHeight="1" ht="24">
-      <c r="A2" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="B2" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" customHeight="1" ht="20">
-      <c r="A3" s="3" t="s">
+      <c r="C2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="D2" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="B3" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:5" customHeight="1" ht="20">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D4" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="4" t="s">
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="B5" t="s">
         <v>15</v>
       </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
+        <v>48</v>
+      </c>
+      <c r="B15" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>51</v>
+      </c>
+      <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
+        <v>53</v>
+      </c>
+      <c r="D16" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" t="s">
+        <v>55</v>
+      </c>
+      <c r="B17" t="s">
+        <v>56</v>
+      </c>
+      <c r="C17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" t="s">
+        <v>58</v>
+      </c>
+      <c r="B18" t="s">
+        <v>59</v>
+      </c>
+      <c r="C18" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s">
+        <v>63</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D20" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" t="s">
+        <v>71</v>
+      </c>
+      <c r="D21" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+      <c r="B22" t="s">
+        <v>73</v>
+      </c>
+      <c r="C22" t="s">
+        <v>74</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" t="s">
+        <v>76</v>
+      </c>
+      <c r="B23" t="s">
+        <v>77</v>
+      </c>
+      <c r="C23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+      <c r="C24" t="s">
+        <v>81</v>
+      </c>
+      <c r="D24" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" t="s">
+        <v>85</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="A26" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>89</v>
+      </c>
+      <c r="D26" t="s">
+        <v>90</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
